--- a/data/trans_camb/IP22_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP22_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 11,22</t>
+          <t>-5,06; 12,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 8,36</t>
+          <t>-7,7; 7,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 5,93</t>
+          <t>-10,28; 5,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 17,0</t>
+          <t>-0,05; 15,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 8,85</t>
+          <t>-6,31; 8,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 7,16</t>
+          <t>-8,68; 7,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 11,45</t>
+          <t>-0,25; 11,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 6,25</t>
+          <t>-4,92; 6,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 3,88</t>
+          <t>-7,47; 3,65</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,61; 71,64</t>
+          <t>-20,91; 76,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,05; 55,1</t>
+          <t>-32,79; 48,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-43,02; 41,29</t>
+          <t>-43,49; 40,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 137,26</t>
+          <t>-0,92; 121,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,9; 66,56</t>
+          <t>-32,5; 66,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,58; 56,14</t>
+          <t>-44,02; 56,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 71,48</t>
+          <t>-1,51; 73,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,42; 39,68</t>
+          <t>-23,6; 38,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-36,95; 24,97</t>
+          <t>-35,68; 24,2</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 15,13</t>
+          <t>1,59; 15,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 3,87</t>
+          <t>-8,0; 4,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 9,05</t>
+          <t>-7,66; 8,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 8,28</t>
+          <t>-6,52; 7,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,67; -4,62</t>
+          <t>-17,65; -4,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,24; -7,09</t>
+          <t>-19,59; -7,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 9,05</t>
+          <t>-0,57; 9,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,1; -1,95</t>
+          <t>-11,0; -2,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,6; -2,07</t>
+          <t>-12,41; -2,71</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,25; 87,87</t>
+          <t>6,39; 87,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-33,21; 22,41</t>
+          <t>-33,5; 26,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,14; 53,37</t>
+          <t>-35,03; 52,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,35; 38,38</t>
+          <t>-21,35; 32,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,13; -20,17</t>
+          <t>-56,55; -18,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,39; -30,04</t>
+          <t>-65,99; -30,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 42,51</t>
+          <t>-1,24; 44,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,01; -9,49</t>
+          <t>-42,6; -11,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-48,38; -9,2</t>
+          <t>-47,95; -11,6</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 2,9</t>
+          <t>-12,74; 2,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 3,86</t>
+          <t>-11,48; 4,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,31; -4,19</t>
+          <t>-20,21; -4,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,41; 19,13</t>
+          <t>2,31; 18,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 0,78</t>
+          <t>-14,65; 0,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,67; -3,49</t>
+          <t>-18,6; -3,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 8,41</t>
+          <t>-2,72; 8,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,05; -0,73</t>
+          <t>-10,59; 0,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,16; -6,52</t>
+          <t>-17,69; -6,19</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-42,67; 12,35</t>
+          <t>-43,55; 11,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-38,1; 18,18</t>
+          <t>-38,22; 19,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-69,61; -17,92</t>
+          <t>-67,79; -20,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,76; 86,96</t>
+          <t>7,06; 85,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,53; 3,63</t>
+          <t>-46,37; 3,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-62,63; -15,28</t>
+          <t>-61,94; -14,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 34,93</t>
+          <t>-9,71; 37,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-37,21; -2,11</t>
+          <t>-36,06; 0,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-60,84; -26,08</t>
+          <t>-61,57; -25,83</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 13,16</t>
+          <t>1,03; 12,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 4,03</t>
+          <t>-7,2; 3,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 3,79</t>
+          <t>-8,15; 3,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 11,22</t>
+          <t>-1,83; 11,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 4,11</t>
+          <t>-7,88; 3,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 9,52</t>
+          <t>-4,16; 8,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 10,32</t>
+          <t>1,54; 10,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 2,17</t>
+          <t>-5,79; 2,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 4,6</t>
+          <t>-4,38; 4,5</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,64; 132,94</t>
+          <t>5,6; 117,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,36; 39,08</t>
+          <t>-44,29; 38,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-52,03; 37,25</t>
+          <t>-51,74; 35,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 78,38</t>
+          <t>-9,79; 81,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,4; 29,78</t>
+          <t>-40,3; 29,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,33; 65,9</t>
+          <t>-21,4; 67,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,98; 78,28</t>
+          <t>8,68; 78,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-35,6; 16,42</t>
+          <t>-33,62; 15,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 35,73</t>
+          <t>-26,06; 33,56</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,8</t>
+          <t>0,53; 7,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 1,81</t>
+          <t>-4,98; 1,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 0,04</t>
+          <t>-7,44; 0,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,07; 9,54</t>
+          <t>2,42; 9,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,44; -1,6</t>
+          <t>-8,24; -2,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,98; -2,94</t>
+          <t>-10,1; -3,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,59; 8,0</t>
+          <t>2,64; 7,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,74; -1,04</t>
+          <t>-5,62; -0,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,55; -2,53</t>
+          <t>-7,64; -2,45</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3,34; 43,94</t>
+          <t>3,03; 45,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-23,85; 10,79</t>
+          <t>-23,77; 9,31</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-36,63; 0,63</t>
+          <t>-36,19; 1,46</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8,59; 47,74</t>
+          <t>10,12; 46,98</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-35,27; -8,01</t>
+          <t>-35,32; -10,08</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-42,7; -14,47</t>
+          <t>-42,06; -15,21</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,85; 41,84</t>
+          <t>12,21; 39,42</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-26,34; -5,24</t>
+          <t>-25,87; -4,76</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-34,97; -12,33</t>
+          <t>-35,75; -12,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP22_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP22_R-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8,17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,76</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,48</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,06</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,41</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,17</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,11</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,62</t>
+          <t>-3,26</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,05</t>
+          <t>-2,45</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 12,15</t>
+          <t>0,23; 16,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 7,66</t>
+          <t>-6,18; 8,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 5,6</t>
+          <t>-9,62; 6,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 15,97</t>
+          <t>-4,77; 12,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 8,95</t>
+          <t>-8,14; 7,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 7,77</t>
+          <t>-10,51; 4,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 11,91</t>
+          <t>0,1; 11,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 6,12</t>
+          <t>-4,75; 6,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 3,65</t>
+          <t>-7,41; 3,51</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>48,95%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-10,52%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>17,38%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-0,29%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-12,06%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>48,95%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,65%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-9,71%</t>
+          <t>-16,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-11,21%</t>
+          <t>-13,39%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,91; 76,03</t>
+          <t>0,07; 122,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-32,79; 48,45</t>
+          <t>-30,87; 69,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-43,49; 40,13</t>
+          <t>-47,93; 50,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 121,58</t>
+          <t>-20,25; 76,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,5; 66,99</t>
+          <t>-35,83; 45,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,02; 56,87</t>
+          <t>-45,58; 28,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 73,62</t>
+          <t>1,54; 72,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,6; 38,86</t>
+          <t>-22,77; 38,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-35,68; 24,2</t>
+          <t>-36,97; 23,24</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,93</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-11,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-13,92</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>8,57</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-1,9</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,7</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,93</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-11,0</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-13,63</t>
+          <t>-3,4</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-7,78</t>
+          <t>-9,06</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 15,1</t>
+          <t>-6,62; 7,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 4,54</t>
+          <t>-16,88; -4,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 8,78</t>
+          <t>-19,81; -7,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 7,67</t>
+          <t>1,98; 15,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,65; -4,71</t>
+          <t>-8,32; 4,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,59; -7,23</t>
+          <t>-10,74; 2,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 9,16</t>
+          <t>-0,41; 9,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,0; -2,39</t>
+          <t>-11,17; -2,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,41; -2,71</t>
+          <t>-13,5; -4,67</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-41,19%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-52,1%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>41,86%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-9,3%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-3,42%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-41,19%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-51,04%</t>
+          <t>-16,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-32,8%</t>
+          <t>-38,18%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,39; 87,98</t>
+          <t>-21,25; 31,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-33,5; 26,23</t>
+          <t>-56,86; -20,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,03; 52,07</t>
+          <t>-66,97; -30,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,35; 32,49</t>
+          <t>9,99; 93,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,55; -18,48</t>
+          <t>-33,98; 24,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,99; -30,61</t>
+          <t>-46,13; 14,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 44,71</t>
+          <t>-1,7; 42,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,6; -11,41</t>
+          <t>-42,66; -9,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-47,95; -11,6</t>
+          <t>-52,54; -21,16</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10,58</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-6,93</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-11,33</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-4,98</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-4,15</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-11,94</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10,58</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-6,93</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-11,44</t>
+          <t>-8,26</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-11,7</t>
+          <t>-9,85</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 2,59</t>
+          <t>2,01; 18,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 4,1</t>
+          <t>-14,16; 0,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,21; -4,51</t>
+          <t>-19,36; -3,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 18,57</t>
+          <t>-12,2; 2,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 0,36</t>
+          <t>-12,23; 2,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,6; -3,51</t>
+          <t>-15,85; -0,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 8,83</t>
+          <t>-2,59; 8,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 0,21</t>
+          <t>-11,21; 0,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-17,69; -6,19</t>
+          <t>-15,02; -4,01</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>40,13%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-26,29%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-42,94%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-19,05%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-15,88%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-45,7%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>40,13%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-26,29%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-43,38%</t>
+          <t>-31,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-44,56%</t>
+          <t>-37,52%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-43,55; 11,46</t>
+          <t>5,32; 83,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-38,22; 19,77</t>
+          <t>-45,95; 3,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-67,79; -20,23</t>
+          <t>-64,77; -15,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,06; 85,33</t>
+          <t>-43,86; 8,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,37; 3,59</t>
+          <t>-39,28; 12,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-61,94; -14,54</t>
+          <t>-53,64; -1,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 37,14</t>
+          <t>-8,71; 38,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-36,06; 0,96</t>
+          <t>-37,9; 3,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-61,57; -25,83</t>
+          <t>-51,79; -17,11</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5,03</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-2,11</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,38</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>6,85</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-1,47</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-2,57</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,03</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-2,11</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,12</t>
+          <t>-3,66</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>-1,1</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 12,9</t>
+          <t>-1,96; 10,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 3,99</t>
+          <t>-8,43; 3,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 3,63</t>
+          <t>-5,23; 7,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 11,47</t>
+          <t>1,11; 12,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 3,97</t>
+          <t>-6,78; 4,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 8,86</t>
+          <t>-8,87; 1,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,54; 10,08</t>
+          <t>1,36; 10,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 2,0</t>
+          <t>-6,09; 1,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 4,5</t>
+          <t>-5,15; 3,19</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>29,58%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-12,42%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8,11%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>51,32%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-10,99%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-19,21%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>29,58%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-12,42%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>-27,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-0,33%</t>
+          <t>-7,25%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,6; 117,88</t>
+          <t>-8,77; 75,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-44,29; 38,24</t>
+          <t>-42,41; 24,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-51,74; 35,42</t>
+          <t>-26,73; 54,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 81,58</t>
+          <t>3,71; 123,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,3; 29,72</t>
+          <t>-41,73; 41,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,4; 67,22</t>
+          <t>-55,05; 19,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,68; 78,41</t>
+          <t>7,64; 78,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-33,62; 15,07</t>
+          <t>-35,25; 13,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-26,06; 33,56</t>
+          <t>-30,64; 23,71</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5,83</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-4,99</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-6,66</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>4,28</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-1,72</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-3,8</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5,83</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-4,99</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-6,39</t>
+          <t>-4,08</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-5,14</t>
+          <t>-5,41</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,53; 7,88</t>
+          <t>2,42; 9,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 1,57</t>
+          <t>-8,45; -1,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 0,4</t>
+          <t>-9,87; -2,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,42; 9,52</t>
+          <t>0,78; 7,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,24; -2,03</t>
+          <t>-5,13; 1,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,1; -3,14</t>
+          <t>-7,66; -0,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,72</t>
+          <t>2,28; 7,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,62; -0,92</t>
+          <t>-5,78; -1,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,64; -2,45</t>
+          <t>-7,96; -2,84</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>26,85%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-22,97%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-30,64%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>22,13%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-8,88%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-19,66%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>26,85%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-22,97%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-29,43%</t>
+          <t>-21,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-24,99%</t>
+          <t>-26,31%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3,03; 45,74</t>
+          <t>10,04; 46,86</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 9,31</t>
+          <t>-35,6; -8,79</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 1,46</t>
+          <t>-42,17; -14,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10,12; 46,98</t>
+          <t>3,46; 43,03</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-35,32; -10,08</t>
+          <t>-24,9; 7,83</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-42,06; -15,21</t>
+          <t>-35,97; -4,19</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,21; 39,42</t>
+          <t>10,12; 39,47</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-25,87; -4,76</t>
+          <t>-26,27; -5,3</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-35,75; -12,64</t>
+          <t>-36,19; -14,46</t>
         </is>
       </c>
     </row>
